--- a/logs/most_important_angle/2_head_model/most_important_angle_analysis.xlsx
+++ b/logs/most_important_angle/2_head_model/most_important_angle_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/most_important_angle/2_head_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66B0DA0-AE62-4D8E-ABDE-FE04C5143B4D}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D64B7BE-A502-44C5-9A4C-D1587E625A8C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="33165" yWindow="1020" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -809,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -818,7 +818,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7155,7 +7154,7 @@
         <v>7.8772846397098008E-3</v>
       </c>
       <c r="BY2" t="str">
-        <f t="shared" ref="BY2:BY33" si="0">CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W2,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
+        <f>CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W2,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
         <v>lambda</v>
       </c>
     </row>
@@ -7386,7 +7385,7 @@
         <v>-0.27902817845106642</v>
       </c>
       <c r="BY3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="BY2:BY33" si="0">CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W3,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
         <v>lambda</v>
       </c>
     </row>
@@ -20857,37 +20856,37 @@
       <c r="A2" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>0.74235773032315966</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>-0.27034447550631091</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>0.81494937187722072</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2">
         <v>0.62483668654098767</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2">
         <v>0.83785952475937031</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2">
         <v>0.69178533811505638</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>6.9084118742846366E-3</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>0.26366136608588808</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>-0.70013749974756767</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>-0.65181018023785975</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2">
         <v>10</v>
       </c>
     </row>
@@ -20895,37 +20894,37 @@
       <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>0.7554947202327964</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>7.4726022646395135E-2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>0.72786529865645522</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3">
         <v>0.68288900521553075</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3">
         <v>0.8339127236086904</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3">
         <v>0.77731185345050668</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>0.48944277834410937</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3">
         <v>0.37304276680204046</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>-0.23550973134106376</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3">
         <v>-0.3280717232195175</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3">
         <v>10</v>
       </c>
     </row>
@@ -20933,37 +20932,37 @@
       <c r="A4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>5.6089753597806866E-2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>4.2992878580178744E-2</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>-8.1991745204695723E-2</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>2.9723671071883773E-2</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4">
         <v>0.26851504534765458</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>8.1120431763802708E-3</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>-9.3345834904157793E-2</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>5.8565537335057483E-2</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>0.28937288618384838</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>-8.2621074294040711E-2</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4">
         <v>10</v>
       </c>
     </row>
@@ -20971,37 +20970,37 @@
       <c r="A5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>5.6162320898373717E-2</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>4.2403138218049738E-2</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>-8.2018123790073158E-2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>2.9790353107624713E-2</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5">
         <v>0.26889483181052498</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>7.9822224654095102E-3</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>-9.2670533419645679E-2</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>5.8801872846189741E-2</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>0.28850657820543429</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>-8.5025364759784519E-2</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5">
         <v>10</v>
       </c>
     </row>
@@ -21009,37 +21008,37 @@
       <c r="A6" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>0.68777082634225095</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>0.4506022194758274</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>0.71390852782950132</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>0.68932467025075073</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6">
         <v>0.81696150540184398</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>0.53088860188690423</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>0.60977901362965004</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>0.62293782246604623</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>0.76833554407143134</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>-0.1986435022638201</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>10</v>
       </c>
     </row>
@@ -21047,37 +21046,37 @@
       <c r="A7" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>0.67142682395090458</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>0.40247929315529091</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>0.66324270647397299</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
         <v>0.7596521667794186</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7">
         <v>0.77562822324009451</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7">
         <v>0.48718419931013096</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>0.66567488046558054</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7">
         <v>0.65966903505893648</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7">
         <v>0.68918305070612085</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7">
         <v>-0.40460979360947713</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7">
         <v>10</v>
       </c>
     </row>
@@ -21085,37 +21084,37 @@
       <c r="A8" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>0.49488369589088194</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>0.12380984609490522</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>0.45932600597373013</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8">
         <v>0.46936942549436583</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8">
         <v>0.63362864236136296</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8">
         <v>0.41721070973406482</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>0.26429811933163688</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8">
         <v>0.33944640009902638</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>0.18329180467970063</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>-0.29179693973074988</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>60</v>
       </c>
     </row>
